--- a/artfynd/A 52544-2020 artfynd.xlsx
+++ b/artfynd/A 52544-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 52544-2020 artfynd.xlsx
+++ b/artfynd/A 52544-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2600,6 +2600,130 @@
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>122511268</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57532</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Bjällermossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>362988</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6352119</v>
+      </c>
+      <c r="S20" t="n">
+        <v>100</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Gunnarsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-02-07</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-02-07</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Angie Cederlund</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Angie Cederlund</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52544-2020 artfynd.xlsx
+++ b/artfynd/A 52544-2020 artfynd.xlsx
@@ -2620,11 +2620,6 @@
       <c r="E20" t="n">
         <v>103021</v>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>Poecile montanus</t>

--- a/artfynd/A 52544-2020 artfynd.xlsx
+++ b/artfynd/A 52544-2020 artfynd.xlsx
@@ -2605,7 +2605,7 @@
         <v>122511268</v>
       </c>
       <c r="B20" t="n">
-        <v>57532</v>
+        <v>57536</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2619,6 +2619,11 @@
       </c>
       <c r="E20" t="n">
         <v>103021</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>

--- a/artfynd/A 52544-2020 artfynd.xlsx
+++ b/artfynd/A 52544-2020 artfynd.xlsx
@@ -2605,7 +2605,7 @@
         <v>122511268</v>
       </c>
       <c r="B20" t="n">
-        <v>57536</v>
+        <v>57537</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
